--- a/光伏配储项目/电价数据/2026/宁西站.xlsx
+++ b/光伏配储项目/电价数据/2026/宁西站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51413</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75382</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57809</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59087</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52479</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10088</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11244</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10374</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12334</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09592000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.14884</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.1946</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09081</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.11554</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.08896</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14798</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21456</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23951</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22591</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.20541</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.03328</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.58663</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13366</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.59751</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.50668</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5194800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.37634</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.56971</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56759</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.61358</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8091799999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6495599999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7584500000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.02492</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66674</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5876699999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.78001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.74549</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.80349</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6470499999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48098</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47223</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42607</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69824</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87524</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.55602</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51754</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48679</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.87022</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51086</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.75826</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.02049</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.66353</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8232999999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.75834</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.66889</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.73993</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5602999999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.91549</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.85142</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.49906</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48917</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.66539</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.58708</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.59126</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.58801</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.6072799999999999</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.7915599999999999</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.5698799999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.8038500000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5709500000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6768099999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.8442000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.72824</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.68657</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.65612</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7734099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.51336</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.30957</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76673</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43913</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5133799999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50828</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5379700000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.47773</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41841</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47368</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21897</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.05309</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7430099999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.22924</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.5672999999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5209199999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.50084</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.57038</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.64722</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6580199999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.63688</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47536</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54645</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5726100000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.9129299999999999</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54199</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62283</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.63328</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5857599999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43113</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44263</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46587</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34217</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5269400000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49223</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5801000000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45501</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.08234</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23262</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.24229</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5317499999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.5267500000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.5464199999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48856</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48695</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.51485</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47544</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.54371</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.8561599999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5499700000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32866</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.48511</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04462</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03229</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22251</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20525</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03915</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05635</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10348</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35019</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65967</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.75407</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.11015</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.45463</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04518</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.18305</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.18158</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04738000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04785</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19984</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14277</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33502</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31701</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17237</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22652</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15645</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220599999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92045</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91459</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86373</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29685</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88855</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63183</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18813</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.52966</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3319</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03365</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5318099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79183</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77383</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7782100000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87688</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8743099999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49394</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40094</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20804</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55106</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62288</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53859</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45597</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45272</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5947899999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59934</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6757000000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57913</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86649</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6190099999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.88727</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.84123</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86233</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7141900000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40778</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35282</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91565</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46222</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49613</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16815</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19112</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59027</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8882599999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.58241</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14679</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6975800000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7878999999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65246</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57214</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49662</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43109</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.57938</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.20925</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.8361799999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5696100000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78975</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32215</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.18333</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23948</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15274</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1553</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16204</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.01501</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.06211999999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14484</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14468</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14721</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.14679</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11529</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11435</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14567</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15114</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44566</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44004</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44286</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34714</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53242</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46439</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26641</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20675</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24443</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35888</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.51124</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.6684500000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.81052</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.7967000000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.42309</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.7814500000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.64878</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.64486</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.93377</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.6723899999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.7844800000000001</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.61351</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42101</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43645</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42217</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69302</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5170800000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34818</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34897</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65686</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7609900000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34364</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7586499999999999</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.65518</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.65716</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.64771</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.65874</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.67176</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26139</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.45137</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.66504</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.67138</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.66586</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.67577</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.6764199999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.6845599999999999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63381</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59738</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59436</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46601</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7307100000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8012100000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42778</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.8517</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48615</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.51314</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6872699999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41413</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55225</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.8284400000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.08667</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.9896200000000001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.84236</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.30426</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.3322</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.7944500000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.21078</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.9578099999999999</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.9248099999999999</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.88717</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>1.18877</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.8737200000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.8662300000000001</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.8800800000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.89416</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.93025</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.20917</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.91459</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.89302</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.12053</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.88671</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.8942100000000001</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43614</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5370199999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6850700000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70904</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.71476</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.52627</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80071</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58148</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5240199999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.82847</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77474</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62486</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67461</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47257</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48036</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47365</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46738</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54977</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45334</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45144</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20921</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.01732</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45798</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18105</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36235</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.84334</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.84239</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.19295</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.84051</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.8432799999999999</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.84468</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22237</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.84527</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.84797</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.84409</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25051</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.84754</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.8350599999999999</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04231</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>1.20425</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.8647100000000001</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.81802</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34705</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18086</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24102</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00069</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12769</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.00034</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03932</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01445</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03992</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03707999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04794</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04747</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02465</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02549</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02659</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04926</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03988000000000001</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20152</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25885</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.54515</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.21553</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.83568</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.83889</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26398</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.82565</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.74482</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7416699999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8400700000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.22549</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.46683</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.8356399999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.46558</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.45682</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.01493</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.46561</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.84635</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01663</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.19293</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20122</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17088</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.17842</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>1.19024</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.8522999999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.85333</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8528</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.87571</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.94062</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.81565</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.68076</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.81471</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.81909</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.03697</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.16814</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.9917100000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.9802799999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.8445199999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.08681</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.07488</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8438300000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.35451</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.50989</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.51688</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.35334</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.84336</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32154</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.46399</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.82214</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.62576</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.56316</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.49563</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.06619</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.52203</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53235</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.60249</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.85494</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.47362</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.46561</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.46984</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43468</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.46445</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14183</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46601</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.46125</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>1.17943</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.8472499999999999</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.85072</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.85129</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.85077</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.46905</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.46795</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.60039</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.84694</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.84614</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.84538</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.84594</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.84593</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1.17457</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.84602</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>1.17446</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>1.17436</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>1.34891</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.42889</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.36341</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>1.38129</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>1.42957</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16953</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.83227</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.84196</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.17491</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.84209</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>1.16927</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.8407899999999999</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.46556</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.52673</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3531</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1.27711</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.63737</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.54533</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.82362</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.17205</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.64018</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4961</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.85117</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.8508600000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.8492999999999999</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.85366</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.47202</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.84702</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.60073</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.46801</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.46772</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.85287</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.8603999999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.85402</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.17513</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.8422000000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84612</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8765499999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.99122</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8596699999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.8645900000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.19358</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.18721</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.17911</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.17787</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.84929</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8546900000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.8452999999999999</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8421900000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.8492999999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.84475</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.8414700000000001</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.67261</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.65139</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.65365</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36733</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45998</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.47163</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.84601</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.84601</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.5007200000000001</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.85287</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.85327</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.85246</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.86081</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.84704</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.85027</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.32082</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.49901</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.18313</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.85263</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.85376</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>1.3202</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>1.34037</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>1.34912</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>1.17907</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.8541799999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.85227</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.8560399999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.85399</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.61358</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.18788</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.3877</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.38001</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.38837</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.36893</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.39184</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.18651</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.18775</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.85545</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.19678</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.86295</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.85415</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.83924</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.17877</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.85822</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.13967</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.84804</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.1896</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.70611</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8403400000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.8448</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37174</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.5699299999999999</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.58029</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.60549</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.57916</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.58262</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.58904</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.8649</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.8627999999999999</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.8796</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.87095</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.48385</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.01807</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.30262</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.26346</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.86033</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.05768</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.87551</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.08449</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.8676900000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.8676699999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1.18671</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.8637400000000001</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.59812</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.86013</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.18775</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.85991</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.8642300000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.86176</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.37054</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.19448</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.86187</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.60448</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.85182</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.58482</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.86542</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.85104</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.8522799999999999</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.86053</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.18187</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.85648</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.1804</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.8572000000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.85087</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.85158</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.85246</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.8610099999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.85212</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.57656</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36702</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.92843</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.51718</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.51096</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.60864</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.63601</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.18797</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.85839</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.8569199999999999</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.8471599999999999</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.35672</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.36776</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.35867</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.69946</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>1.42583</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.02053</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1.15433</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8631</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.74207</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.53471</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.64763</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6507000000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49705</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.47586</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.57136</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.67822</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.85202</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.62422</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.60995</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.59253</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.77708</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.58924</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.58714</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.8492000000000001</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.85638</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.8605900000000001</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.86127</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.19312</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.17522</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.86614</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.8593</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.59016</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.59434</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.9923099999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.59099</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.84835</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36151</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.75103</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.5738300000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.5729099999999999</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.15777</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14408</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19923</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.26143</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.61019</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5379299999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.1723</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.45755</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.5063799999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.13504</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.57551</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.62227</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12922</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21233</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.45318</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.45756</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.47218</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47721</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37596</v>
       </c>
     </row>
   </sheetData>
